--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126683570</v>
+        <v>126683553</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607799</v>
+        <v>607811</v>
       </c>
       <c r="R8" t="n">
-        <v>6959220</v>
+        <v>6959155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126683553</v>
+        <v>126683570</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607811</v>
+        <v>607799</v>
       </c>
       <c r="R9" t="n">
-        <v>6959155</v>
+        <v>6959220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
         <v>126683567</v>
       </c>
       <c r="B11" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126683569</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126683571</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126683566</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,32 +2404,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683550</v>
+        <v>126683559</v>
       </c>
       <c r="B19" t="n">
-        <v>91210</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607806</v>
+        <v>608012</v>
       </c>
       <c r="R19" t="n">
-        <v>6959160</v>
+        <v>6959123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2504,7 +2509,7 @@
         <v>126683574</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2598,32 +2603,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683559</v>
+        <v>126683550</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>91284</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608012</v>
+        <v>607806</v>
       </c>
       <c r="R21" t="n">
-        <v>6959123</v>
+        <v>6959160</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,11 +2674,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
         <v>126683552</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>126683573</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>126683577</v>
       </c>
       <c r="B27" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126683553</v>
+        <v>126675986</v>
       </c>
       <c r="B8" t="n">
-        <v>91319</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607811</v>
+        <v>607776</v>
       </c>
       <c r="R8" t="n">
-        <v>6959155</v>
+        <v>6959090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,7 +1417,7 @@
         <v>126683570</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126675986</v>
+        <v>126683553</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607776</v>
+        <v>607811</v>
       </c>
       <c r="R10" t="n">
-        <v>6959090</v>
+        <v>6959155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,7 +1611,7 @@
         <v>126683567</v>
       </c>
       <c r="B11" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126683569</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126683571</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126683566</v>
       </c>
       <c r="B15" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,32 +2404,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683559</v>
+        <v>126683550</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>91290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>608012</v>
+        <v>607806</v>
       </c>
       <c r="R19" t="n">
-        <v>6959123</v>
+        <v>6959160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,11 +2475,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126683574</v>
+        <v>126683559</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607780</v>
+        <v>608012</v>
       </c>
       <c r="R20" t="n">
-        <v>6959113</v>
+        <v>6959123</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,6 +2572,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,10 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683550</v>
+        <v>126683574</v>
       </c>
       <c r="B21" t="n">
-        <v>91284</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2614,21 +2614,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607806</v>
+        <v>607780</v>
       </c>
       <c r="R21" t="n">
-        <v>6959160</v>
+        <v>6959113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
         <v>126683552</v>
       </c>
       <c r="B23" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>126683573</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>126683577</v>
       </c>
       <c r="B27" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126675986</v>
+        <v>126683570</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,39 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607776</v>
+        <v>607799</v>
       </c>
       <c r="R8" t="n">
-        <v>6959090</v>
+        <v>6959220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126683570</v>
+        <v>126675986</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607799</v>
+        <v>607776</v>
       </c>
       <c r="R9" t="n">
-        <v>6959220</v>
+        <v>6959090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126683566</v>
+        <v>126683555</v>
       </c>
       <c r="B15" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,21 +2012,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607814</v>
+        <v>607763</v>
       </c>
       <c r="R15" t="n">
-        <v>6959175</v>
+        <v>6959147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2098,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126683555</v>
+        <v>126683566</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>91621</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607763</v>
+        <v>607814</v>
       </c>
       <c r="R16" t="n">
-        <v>6959147</v>
+        <v>6959175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,11 +2174,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126683570</v>
+        <v>126683553</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607799</v>
+        <v>607811</v>
       </c>
       <c r="R8" t="n">
-        <v>6959220</v>
+        <v>6959155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126683553</v>
+        <v>126683570</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607811</v>
+        <v>607799</v>
       </c>
       <c r="R10" t="n">
-        <v>6959155</v>
+        <v>6959220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683550</v>
+        <v>126683574</v>
       </c>
       <c r="B19" t="n">
-        <v>91290</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607806</v>
+        <v>607780</v>
       </c>
       <c r="R19" t="n">
-        <v>6959160</v>
+        <v>6959113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126683559</v>
+        <v>126683550</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>91290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>608012</v>
+        <v>607806</v>
       </c>
       <c r="R20" t="n">
-        <v>6959123</v>
+        <v>6959160</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,11 +2572,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683574</v>
+        <v>126683559</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607780</v>
+        <v>608012</v>
       </c>
       <c r="R21" t="n">
-        <v>6959113</v>
+        <v>6959123</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,6 +2669,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>126683553</v>
       </c>
       <c r="B8" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>126683567</v>
       </c>
       <c r="B11" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126683555</v>
+        <v>126683566</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>91622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,21 +2012,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607763</v>
+        <v>607814</v>
       </c>
       <c r="R15" t="n">
-        <v>6959147</v>
+        <v>6959175</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2072,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126683566</v>
+        <v>126683555</v>
       </c>
       <c r="B16" t="n">
-        <v>91621</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2109,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607814</v>
+        <v>607763</v>
       </c>
       <c r="R16" t="n">
-        <v>6959175</v>
+        <v>6959147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,6 +2169,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Färska spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,7 +2407,7 @@
         <v>126683574</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>126683550</v>
       </c>
       <c r="B20" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126683552</v>
       </c>
       <c r="B23" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>126683577</v>
       </c>
       <c r="B27" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126683553</v>
+        <v>126683570</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607811</v>
+        <v>607799</v>
       </c>
       <c r="R8" t="n">
-        <v>6959155</v>
+        <v>6959220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126675986</v>
+        <v>126683553</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,39 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607776</v>
+        <v>607811</v>
       </c>
       <c r="R9" t="n">
-        <v>6959090</v>
+        <v>6959155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126683570</v>
+        <v>126675986</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1512,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607799</v>
+        <v>607776</v>
       </c>
       <c r="R10" t="n">
-        <v>6959220</v>
+        <v>6959090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683574</v>
+        <v>126683550</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>91291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607780</v>
+        <v>607806</v>
       </c>
       <c r="R19" t="n">
-        <v>6959113</v>
+        <v>6959160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126683550</v>
+        <v>126683559</v>
       </c>
       <c r="B20" t="n">
-        <v>91291</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607806</v>
+        <v>608012</v>
       </c>
       <c r="R20" t="n">
-        <v>6959160</v>
+        <v>6959123</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,6 +2572,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,32 +2603,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683559</v>
+        <v>126683574</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608012</v>
+        <v>607780</v>
       </c>
       <c r="R21" t="n">
-        <v>6959123</v>
+        <v>6959113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,11 +2674,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126683570</v>
+        <v>126683553</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607799</v>
+        <v>607811</v>
       </c>
       <c r="R8" t="n">
-        <v>6959220</v>
+        <v>6959155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126683553</v>
+        <v>126683570</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607811</v>
+        <v>607799</v>
       </c>
       <c r="R9" t="n">
-        <v>6959155</v>
+        <v>6959220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126683559</v>
+        <v>126683574</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>608012</v>
+        <v>607780</v>
       </c>
       <c r="R20" t="n">
-        <v>6959123</v>
+        <v>6959113</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,11 +2572,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683574</v>
+        <v>126683559</v>
       </c>
       <c r="B21" t="n">
-        <v>98360</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607780</v>
+        <v>608012</v>
       </c>
       <c r="R21" t="n">
-        <v>6959113</v>
+        <v>6959123</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,6 +2669,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>126675986</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>126675986</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1504,7 +1504,7 @@
         <v>126675986</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>126683553</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>91319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>126683570</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>126683567</v>
       </c>
       <c r="B11" t="n">
-        <v>97321</v>
+        <v>97314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126683569</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126683571</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126683566</v>
       </c>
       <c r="B15" t="n">
-        <v>91622</v>
+        <v>91615</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,32 +2404,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683550</v>
+        <v>126683559</v>
       </c>
       <c r="B19" t="n">
-        <v>91291</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607806</v>
+        <v>608012</v>
       </c>
       <c r="R19" t="n">
-        <v>6959160</v>
+        <v>6959123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2504,7 +2509,7 @@
         <v>126683574</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2598,32 +2603,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683559</v>
+        <v>126683550</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>91284</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608012</v>
+        <v>607806</v>
       </c>
       <c r="R21" t="n">
-        <v>6959123</v>
+        <v>6959160</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,11 +2674,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
         <v>126683552</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>91319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>126683573</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>126683577</v>
       </c>
       <c r="B27" t="n">
-        <v>88729</v>
+        <v>88722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -1310,7 +1310,7 @@
         <v>126683553</v>
       </c>
       <c r="B8" t="n">
-        <v>91319</v>
+        <v>91326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>126683570</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>126683567</v>
       </c>
       <c r="B11" t="n">
-        <v>97314</v>
+        <v>97321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126683569</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>126683571</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126683566</v>
       </c>
       <c r="B15" t="n">
-        <v>91615</v>
+        <v>91622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,32 +2404,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683559</v>
+        <v>126683550</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>91291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>608012</v>
+        <v>607806</v>
       </c>
       <c r="R19" t="n">
-        <v>6959123</v>
+        <v>6959160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,11 +2475,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,7 +2504,7 @@
         <v>126683574</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683550</v>
+        <v>126683559</v>
       </c>
       <c r="B21" t="n">
-        <v>91284</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607806</v>
+        <v>608012</v>
       </c>
       <c r="R21" t="n">
-        <v>6959160</v>
+        <v>6959123</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,6 +2669,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
         <v>126683552</v>
       </c>
       <c r="B23" t="n">
-        <v>91319</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>126683573</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>126683577</v>
       </c>
       <c r="B27" t="n">
-        <v>88722</v>
+        <v>88729</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117140357</v>
+        <v>126683577</v>
       </c>
       <c r="B2" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607971</v>
+        <v>607857</v>
       </c>
       <c r="R2" t="n">
-        <v>6959234</v>
+        <v>6959114</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,37 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117140359</v>
+        <v>126683566</v>
       </c>
       <c r="B3" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607876</v>
+        <v>607814</v>
       </c>
       <c r="R3" t="n">
-        <v>6959144</v>
+        <v>6959175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,31 +861,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117140363</v>
+        <v>117140359</v>
       </c>
       <c r="B4" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607839</v>
+        <v>607876</v>
       </c>
       <c r="R4" t="n">
-        <v>6959281</v>
+        <v>6959144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,12 +977,7 @@
         <v>117140360</v>
       </c>
       <c r="B5" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,37 +1075,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117140361</v>
+        <v>126683552</v>
       </c>
       <c r="B6" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608010</v>
+        <v>607854</v>
       </c>
       <c r="R6" t="n">
-        <v>6959123</v>
+        <v>6959284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,26 +1160,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126683565</v>
+        <v>126683553</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607855</v>
+        <v>607811</v>
       </c>
       <c r="R7" t="n">
-        <v>6959164</v>
+        <v>6959155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1243,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.  Sitter högt upp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1269,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126683553</v>
+        <v>126683550</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607811</v>
+        <v>607806</v>
       </c>
       <c r="R8" t="n">
-        <v>6959155</v>
+        <v>6959160</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,14 +1366,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126683570</v>
+        <v>117140357</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1439,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607799</v>
+        <v>607971</v>
       </c>
       <c r="R9" t="n">
-        <v>6959220</v>
+        <v>6959234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,12 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,62 +1451,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126675986</v>
+        <v>117140362</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607776</v>
+        <v>608004</v>
       </c>
       <c r="R10" t="n">
-        <v>6959090</v>
+        <v>6959182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,17 +1532,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,44 +1552,48 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126683567</v>
+        <v>126683569</v>
       </c>
       <c r="B11" t="n">
-        <v>97321</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607816</v>
+        <v>607880</v>
       </c>
       <c r="R11" t="n">
-        <v>6959170</v>
+        <v>6959168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,14 +1665,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126683569</v>
+        <v>126683570</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1740,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607880</v>
+        <v>607799</v>
       </c>
       <c r="R12" t="n">
-        <v>6959168</v>
+        <v>6959220</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,11 +1765,11 @@
         <v>126683571</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1899,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126683563</v>
+        <v>126683573</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607893</v>
+        <v>607781</v>
       </c>
       <c r="R14" t="n">
-        <v>6959185</v>
+        <v>6959096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126683566</v>
+        <v>117140363</v>
       </c>
       <c r="B15" t="n">
-        <v>91622</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607814</v>
+        <v>607839</v>
       </c>
       <c r="R15" t="n">
-        <v>6959175</v>
+        <v>6959281</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,12 +2021,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2086,22 +2041,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126683555</v>
+        <v>126675986</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,16 +2086,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607763</v>
+        <v>607776</v>
       </c>
       <c r="R16" t="n">
-        <v>6959147</v>
+        <v>6959090</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2137,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126683557</v>
+        <v>126683555</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607869</v>
+        <v>607763</v>
       </c>
       <c r="R17" t="n">
-        <v>6959106</v>
+        <v>6959147</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126683560</v>
+        <v>126683557</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,10 +2301,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607946</v>
+        <v>607869</v>
       </c>
       <c r="R18" t="n">
-        <v>6959127</v>
+        <v>6959106</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2341,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Äldre spår</t>
+          <t>Ringhack på tall. Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,32 +2368,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126683550</v>
+        <v>126683558</v>
       </c>
       <c r="B19" t="n">
-        <v>91291</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607806</v>
+        <v>607909</v>
       </c>
       <c r="R19" t="n">
-        <v>6959160</v>
+        <v>6959122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,6 +2439,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Färska spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,32 +2470,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126683574</v>
+        <v>126683559</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2505,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607780</v>
+        <v>608012</v>
       </c>
       <c r="R20" t="n">
-        <v>6959113</v>
+        <v>6959123</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,6 +2541,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,10 +2572,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126683559</v>
+        <v>126683560</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608012</v>
+        <v>607946</v>
       </c>
       <c r="R21" t="n">
-        <v>6959123</v>
+        <v>6959127</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,7 +2647,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Både färska och äldre spår</t>
+          <t>Ringhack på tall. Äldre spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,7 +2677,7 @@
         <v>126683561</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2802,10 +2776,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126683552</v>
+        <v>126683563</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,21 +2787,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2837,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607854</v>
+        <v>607893</v>
       </c>
       <c r="R23" t="n">
-        <v>6959284</v>
+        <v>6959185</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,6 +2847,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2899,10 +2878,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126683558</v>
+        <v>126683564</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607909</v>
+        <v>607815</v>
       </c>
       <c r="R24" t="n">
-        <v>6959122</v>
+        <v>6959273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,7 +2953,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Färska spår</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3001,10 +2980,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126683573</v>
+        <v>126683565</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,21 +2991,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3036,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607781</v>
+        <v>607855</v>
       </c>
       <c r="R25" t="n">
-        <v>6959096</v>
+        <v>6959164</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3072,6 +3051,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.  Sitter högt upp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3098,32 +3082,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126683564</v>
+        <v>126683574</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3133,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607815</v>
+        <v>607780</v>
       </c>
       <c r="R26" t="n">
-        <v>6959273</v>
+        <v>6959113</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,11 +3153,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3200,48 +3179,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126683577</v>
+        <v>117140361</v>
       </c>
       <c r="B27" t="n">
-        <v>88729</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607857</v>
+        <v>608010</v>
       </c>
       <c r="R27" t="n">
-        <v>6959114</v>
+        <v>6959123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,12 +3244,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,22 +3258,122 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126683567</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storsvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>607816</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6959170</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30267-2025 artfynd.xlsx
+++ b/artfynd/A 30267-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683566</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140360</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683553</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683550</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140357</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140362</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683570</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683571</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683573</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140363</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126675986</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683555</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683557</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2467,6 +2557,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683558</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2569,6 +2664,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683559</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2671,6 +2771,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683560</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2773,6 +2878,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683561</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2875,6 +2985,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683563</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2977,6 +3092,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683564</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3079,6 +3199,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683565</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3176,6 +3301,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683574</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3277,6 +3407,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140361</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3374,8 +3509,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>